--- a/Improved_Bus_Planning_version_B.xlsx
+++ b/Improved_Bus_Planning_version_B.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H354"/>
+  <dimension ref="A1:H334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,7 +644,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -9130,31 +9130,33 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>16:20:00</t>
+          <t>16:21:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:44:00</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>400</v>
+      </c>
       <c r="G230" t="n">
-        <v>1.98</v>
+        <v>12.8496</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -9171,12 +9173,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>16:21:00</t>
+          <t>16:24:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>16:44:00</t>
+          <t>16:47:00</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -9192,29 +9194,29 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:26:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>16:47:00</t>
+          <t>16:51:00</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9223,10 +9225,10 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G232" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9247,12 +9249,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>16:26:00</t>
+          <t>16:27:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>16:51:00</t>
+          <t>16:50:00</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9261,36 +9263,36 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G233" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>16:27:00</t>
+          <t>16:29:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>16:50:00</t>
+          <t>16:53:00</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9299,36 +9301,36 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>16:29:00</t>
+          <t>16:34:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>16:53:00</t>
+          <t>16:57:00</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9337,14 +9339,14 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G235" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -9361,12 +9363,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>16:34:00</t>
+          <t>16:36:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>16:57:00</t>
+          <t>17:01:00</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -9375,26 +9377,26 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9404,7 +9406,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>17:01:00</t>
+          <t>16:59:00</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -9413,14 +9415,14 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G237" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9439,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>16:39:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>16:59:00</t>
+          <t>17:03:00</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -9451,72 +9453,74 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G238" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:46:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>16:39:00</t>
+          <t>17:11:00</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>401</v>
+      </c>
       <c r="G239" t="n">
-        <v>-112.5</v>
+        <v>10.86</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>16:39:00</t>
+          <t>16:49:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>17:03:00</t>
+          <t>17:12:00</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -9525,36 +9529,36 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G240" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>16:46:00</t>
+          <t>16:49:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>17:11:00</t>
+          <t>17:13:00</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -9566,33 +9570,33 @@
         <v>401</v>
       </c>
       <c r="G241" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>16:49:00</t>
+          <t>16:51:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>17:12:00</t>
+          <t>17:14:00</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -9604,11 +9608,11 @@
         <v>400</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9629,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>16:49:00</t>
+          <t>16:54:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>17:13:00</t>
+          <t>17:17:00</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -9639,36 +9643,36 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G243" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>16:51:00</t>
+          <t>16:56:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>17:14:00</t>
+          <t>17:21:00</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -9677,36 +9681,36 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G244" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>16:54:00</t>
+          <t>16:57:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>17:17:00</t>
+          <t>17:20:00</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -9718,33 +9722,33 @@
         <v>400</v>
       </c>
       <c r="G245" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>16:56:00</t>
+          <t>16:59:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>17:21:00</t>
+          <t>17:23:00</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9756,11 +9760,11 @@
         <v>401</v>
       </c>
       <c r="G246" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -9777,12 +9781,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>16:57:00</t>
+          <t>17:04:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>17:20:00</t>
+          <t>17:27:00</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9798,29 +9802,29 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>16:59:00</t>
+          <t>17:06:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>17:23:00</t>
+          <t>17:31:00</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9832,33 +9836,33 @@
         <v>401</v>
       </c>
       <c r="G248" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>17:04:00</t>
+          <t>17:06:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>17:27:00</t>
+          <t>17:29:00</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9870,33 +9874,33 @@
         <v>400</v>
       </c>
       <c r="G249" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>17:06:00</t>
+          <t>17:09:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>17:31:00</t>
+          <t>17:33:00</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -9908,33 +9912,33 @@
         <v>401</v>
       </c>
       <c r="G250" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>17:06:00</t>
+          <t>17:16:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>17:29:00</t>
+          <t>17:41:00</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -9943,14 +9947,14 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G251" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -9967,12 +9971,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>17:09:00</t>
+          <t>17:19:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>17:33:00</t>
+          <t>17:43:00</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9988,7 +9992,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -10005,12 +10009,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>17:16:00</t>
+          <t>17:19:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>17:41:00</t>
+          <t>17:42:00</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -10019,14 +10023,14 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G253" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -10038,31 +10042,33 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>17:12:00</t>
+          <t>17:21:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>17:16:00</t>
+          <t>17:44:00</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>400</v>
+      </c>
       <c r="G254" t="n">
-        <v>1.98</v>
+        <v>12.8496</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10085,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>17:19:00</t>
+          <t>17:24:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>17:43:00</t>
+          <t>17:47:00</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -10093,14 +10099,14 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G255" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -10117,12 +10123,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>17:19:00</t>
+          <t>17:26:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>17:42:00</t>
+          <t>17:51:00</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -10131,36 +10137,36 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G256" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>17:21:00</t>
+          <t>17:27:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>17:44:00</t>
+          <t>17:50:00</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10172,11 +10178,11 @@
         <v>400</v>
       </c>
       <c r="G257" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -10193,12 +10199,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>17:24:00</t>
+          <t>17:29:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>17:47:00</t>
+          <t>17:53:00</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -10207,14 +10213,14 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G258" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -10231,12 +10237,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>17:26:00</t>
+          <t>17:34:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>17:51:00</t>
+          <t>17:57:00</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -10245,36 +10251,36 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G259" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>17:27:00</t>
+          <t>17:36:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>17:50:00</t>
+          <t>17:59:00</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -10286,33 +10292,33 @@
         <v>400</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>17:29:00</t>
+          <t>17:36:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>17:53:00</t>
+          <t>18:01:00</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -10324,47 +10330,49 @@
         <v>401</v>
       </c>
       <c r="G261" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>17:16:00</t>
+          <t>17:39:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>17:34:00</t>
+          <t>18:03:00</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>401</v>
+      </c>
       <c r="G262" t="n">
-        <v>-135</v>
+        <v>10.8036</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -10381,12 +10389,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>17:34:00</t>
+          <t>17:46:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>17:57:00</t>
+          <t>18:11:00</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -10395,14 +10403,14 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G263" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10427,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>17:36:00</t>
+          <t>17:49:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>17:59:00</t>
+          <t>18:13:00</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -10433,14 +10441,14 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G264" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -10457,12 +10465,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>17:36:00</t>
+          <t>17:49:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>18:01:00</t>
+          <t>18:12:00</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -10471,14 +10479,14 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G265" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10503,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>17:39:00</t>
+          <t>17:51:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>18:03:00</t>
+          <t>18:14:00</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -10509,36 +10517,36 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G266" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>bus15</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>17:46:00</t>
+          <t>17:54:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>18:11:00</t>
+          <t>18:17:00</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -10547,72 +10555,74 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G267" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>17:42:00</t>
+          <t>17:56:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>17:46:00</t>
+          <t>18:21:00</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>401</v>
+      </c>
       <c r="G268" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>17:49:00</t>
+          <t>17:57:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>18:13:00</t>
+          <t>18:20:00</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -10621,36 +10631,36 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G269" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>17:49:00</t>
+          <t>17:59:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>18:12:00</t>
+          <t>18:23:00</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -10659,72 +10669,74 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G270" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>17:50:00</t>
+          <t>18:04:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>17:54:00</t>
+          <t>18:27:00</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>400</v>
+      </c>
       <c r="G271" t="n">
-        <v>1.98</v>
+        <v>12.3</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>17:51:00</t>
+          <t>18:06:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>18:14:00</t>
+          <t>18:31:00</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -10733,14 +10745,14 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G272" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -10757,12 +10769,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>17:54:00</t>
+          <t>18:07:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>18:17:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -10778,29 +10790,29 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>bus16</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>17:56:00</t>
+          <t>18:14:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>18:21:00</t>
+          <t>18:38:00</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10812,11 +10824,11 @@
         <v>401</v>
       </c>
       <c r="G274" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -10833,12 +10845,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>17:57:00</t>
+          <t>18:16:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>18:20:00</t>
+          <t>18:41:00</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10847,36 +10859,36 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G275" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>17:59:00</t>
+          <t>18:19:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>18:23:00</t>
+          <t>18:42:00</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10885,72 +10897,74 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G276" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>17:46:00</t>
+          <t>18:22:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>18:04:00</t>
+          <t>18:45:00</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>400</v>
+      </c>
       <c r="G277" t="n">
-        <v>-135</v>
+        <v>12.8496</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>18:04:00</t>
+          <t>18:24:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>18:27:00</t>
+          <t>18:47:00</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10962,7 +10976,7 @@
         <v>400</v>
       </c>
       <c r="G278" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -10983,12 +10997,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>18:06:00</t>
+          <t>18:26:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>18:31:00</t>
+          <t>18:51:00</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11004,29 +11018,29 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>18:07:00</t>
+          <t>18:27:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:50:00</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -11038,69 +11052,71 @@
         <v>400</v>
       </c>
       <c r="G280" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>17:54:00</t>
+          <t>18:29:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>18:14:00</t>
+          <t>18:53:00</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>401</v>
+      </c>
       <c r="G281" t="n">
-        <v>-150</v>
+        <v>10.8036</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>18:14:00</t>
+          <t>18:34:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>18:38:00</t>
+          <t>18:57:00</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11109,36 +11125,36 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G282" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18:16:00</t>
+          <t>18:37:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>18:41:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11147,14 +11163,14 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G283" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>bus15</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -11171,12 +11187,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>18:19:00</t>
+          <t>18:41:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>18:42:00</t>
+          <t>19:06:00</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -11185,14 +11201,14 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G284" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -11209,12 +11225,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>18:22:00</t>
+          <t>18:44:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>18:45:00</t>
+          <t>19:08:00</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11223,36 +11239,36 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G285" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>18:24:00</t>
+          <t>18:49:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>18:47:00</t>
+          <t>19:12:00</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11264,33 +11280,33 @@
         <v>400</v>
       </c>
       <c r="G286" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>18:26:00</t>
+          <t>18:52:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>18:51:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11299,36 +11315,36 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G287" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>18:27:00</t>
+          <t>18:54:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>18:50:00</t>
+          <t>19:17:00</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11340,69 +11356,71 @@
         <v>400</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>bus16</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>18:27:00</t>
+          <t>18:56:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>18:31:00</t>
+          <t>19:21:00</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>401</v>
+      </c>
       <c r="G289" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>18:29:00</t>
+          <t>18:57:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>18:53:00</t>
+          <t>19:20:00</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -11411,36 +11429,36 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G290" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>18:34:00</t>
+          <t>18:59:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>18:57:00</t>
+          <t>19:23:00</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -11449,50 +11467,52 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G291" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>18:31:00</t>
+          <t>19:04:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>18:35:00</t>
+          <t>19:27:00</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>400</v>
+      </c>
       <c r="G292" t="n">
-        <v>1.98</v>
+        <v>12.3</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11529,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:37:00</t>
+          <t>19:07:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -11530,7 +11550,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>bus17</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -11547,12 +11567,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>18:41:00</t>
+          <t>19:11:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>19:06:00</t>
+          <t>19:36:00</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -11568,7 +11588,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -11585,12 +11605,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>18:44:00</t>
+          <t>19:14:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>19:08:00</t>
+          <t>19:38:00</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -11606,65 +11626,67 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>bus15</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>18:31:00</t>
+          <t>19:19:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>18:49:00</t>
+          <t>19:42:00</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>400</v>
+      </c>
       <c r="G296" t="n">
-        <v>-135</v>
+        <v>12.3</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>18:49:00</t>
+          <t>19:22:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>19:12:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -11676,83 +11698,87 @@
         <v>400</v>
       </c>
       <c r="G297" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>18:35:00</t>
+          <t>19:26:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>18:52:00</t>
+          <t>19:51:00</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>401</v>
+      </c>
       <c r="G298" t="n">
-        <v>-127.5</v>
+        <v>10.86</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>18:51:00</t>
+          <t>19:27:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>18:55:00</t>
+          <t>19:50:00</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>400</v>
+      </c>
       <c r="G299" t="n">
-        <v>1.98</v>
+        <v>12.3</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11795,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>18:52:00</t>
+          <t>19:29:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:53:00</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -11783,36 +11809,36 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G300" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>18:54:00</t>
+          <t>19:34:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>19:17:00</t>
+          <t>19:57:00</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -11824,33 +11850,33 @@
         <v>400</v>
       </c>
       <c r="G301" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>bus16</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>18:56:00</t>
+          <t>19:37:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>19:21:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -11859,14 +11885,14 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G302" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -11883,12 +11909,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18:57:00</t>
+          <t>19:41:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>19:20:00</t>
+          <t>20:06:00</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -11897,14 +11923,14 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G303" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -11921,12 +11947,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18:59:00</t>
+          <t>19:44:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>19:23:00</t>
+          <t>20:08:00</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -11942,7 +11968,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -11959,12 +11985,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>19:04:00</t>
+          <t>19:49:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>19:27:00</t>
+          <t>20:12:00</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11980,65 +12006,67 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>19:06:00</t>
+          <t>19:56:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>19:10:00</t>
+          <t>20:21:00</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>401</v>
+      </c>
       <c r="G306" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>19:07:00</t>
+          <t>20:04:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:27:00</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -12050,47 +12078,49 @@
         <v>400</v>
       </c>
       <c r="G307" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>bus18</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>18:55:00</t>
+          <t>20:07:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>19:11:00</t>
+          <t>20:31:00</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>401</v>
+      </c>
       <c r="G308" t="n">
-        <v>-120</v>
+        <v>10.8036</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -12107,12 +12137,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>19:11:00</t>
+          <t>20:11:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>19:36:00</t>
+          <t>20:36:00</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -12128,7 +12158,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>bus17</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -12145,12 +12175,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>19:12:00</t>
+          <t>20:12:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>19:16:00</t>
+          <t>20:16:00</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -12164,7 +12194,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -12181,12 +12211,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>19:14:00</t>
+          <t>20:22:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>19:38:00</t>
+          <t>20:46:00</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12202,81 +12232,81 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>bus19</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>19:19:00</t>
+          <t>20:16:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>19:42:00</t>
+          <t>20:35:00</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F312" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
       <c r="G312" t="n">
-        <v>12.3</v>
+        <v>-142.5</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>bus15</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>19:21:00</t>
+          <t>20:35:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>19:25:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>401</v>
+      </c>
       <c r="G313" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -12288,91 +12318,89 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>19:22:00</t>
+          <t>20:27:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>20:31:00</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F314" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
       <c r="G314" t="n">
-        <v>12.8496</v>
+        <v>1.98</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
           <t>ehvgar</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>ehvgar</t>
-        </is>
-      </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>19:10:00</t>
+          <t>20:36:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>19:26:00</t>
+          <t>20:40:00</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>charging</t>
+          <t>material trip</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="n">
-        <v>-120</v>
+        <v>1.98</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>19:26:00</t>
+          <t>20:37:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>19:51:00</t>
+          <t>21:01:00</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -12384,181 +12412,181 @@
         <v>401</v>
       </c>
       <c r="G316" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>19:27:00</t>
+          <t>20:31:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>19:50:00</t>
+          <t>20:46:00</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F317" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="n">
-        <v>12.3</v>
+        <v>-112.5</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>bus16</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>19:27:00</t>
+          <t>20:46:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>19:31:00</t>
+          <t>21:09:00</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>400</v>
+      </c>
       <c r="G318" t="n">
-        <v>1.98</v>
+        <v>12.3</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>19:29:00</t>
+          <t>20:40:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>19:53:00</t>
+          <t>21:05:00</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F319" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
       <c r="G319" t="n">
-        <v>10.8036</v>
+        <v>-187.5</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>bus20</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>19:16:00</t>
+          <t>21:05:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>19:34:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>401</v>
+      </c>
       <c r="G320" t="n">
-        <v>-135</v>
+        <v>10.86</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>19:34:00</t>
+          <t>21:07:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>19:57:00</t>
+          <t>21:31:00</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -12567,36 +12595,36 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G321" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>19:37:00</t>
+          <t>21:35:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -12605,50 +12633,52 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G322" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>bus17</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>19:25:00</t>
+          <t>21:37:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>19:41:00</t>
+          <t>22:01:00</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>401</v>
+      </c>
       <c r="G323" t="n">
-        <v>-120</v>
+        <v>10.8036</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12695,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>19:41:00</t>
+          <t>22:05:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20:06:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -12686,7 +12716,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>bus18</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -12703,12 +12733,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>19:44:00</t>
+          <t>22:07:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20:08:00</t>
+          <t>22:31:00</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -12724,65 +12754,67 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>bus15</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>19:31:00</t>
+          <t>22:35:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>19:49:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>401</v>
+      </c>
       <c r="G326" t="n">
-        <v>-135</v>
+        <v>10.86</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>19:49:00</t>
+          <t>22:37:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20:12:00</t>
+          <t>23:01:00</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -12791,14 +12823,14 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G327" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>bus19</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -12815,12 +12847,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>19:56:00</t>
+          <t>23:05:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20:21:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -12836,29 +12868,29 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20:04:00</t>
+          <t>23:07:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20:27:00</t>
+          <t>23:31:00</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -12867,46 +12899,48 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G329" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>bus20</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>19:57:00</t>
+          <t>23:35:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20:01:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>401</v>
+      </c>
       <c r="G330" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -12927,12 +12961,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>20:07:00</t>
+          <t>23:37:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20:31:00</t>
+          <t>00:01:00</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -12948,7 +12982,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>bus16</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -12965,12 +12999,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>20:11:00</t>
+          <t>00:01:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20:36:00</t>
+          <t>00:26:00</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -12986,837 +13020,83 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>bus17</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>20:01:00</t>
+          <t>00:09:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20:22:00</t>
+          <t>00:33:00</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>401</v>
+      </c>
       <c r="G333" t="n">
-        <v>-157.5</v>
+        <v>10.8036</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>20:21:00</t>
+          <t>00:31:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20:25:00</t>
+          <t>00:56:00</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>401</v>
+      </c>
       <c r="G334" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>bus13</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>20:22:00</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>20:46:00</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F335" t="n">
-        <v>401</v>
-      </c>
-      <c r="G335" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>bus14</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>20:35:00</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F336" t="n">
-        <v>401</v>
-      </c>
-      <c r="G336" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>bus15</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>20:37:00</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>21:01:00</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F337" t="n">
-        <v>401</v>
-      </c>
-      <c r="G337" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>bus18</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>ehvgar</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>ehvgar</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>20:25:00</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>20:46:00</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="n">
-        <v>-157.5</v>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>bus13</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>20:46:00</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>21:09:00</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F339" t="n">
-        <v>400</v>
-      </c>
-      <c r="G339" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>bus16</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>21:05:00</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F340" t="n">
-        <v>401</v>
-      </c>
-      <c r="G340" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>bus14</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>21:07:00</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>21:31:00</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F341" t="n">
-        <v>401</v>
-      </c>
-      <c r="G341" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>bus19</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>21:35:00</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F342" t="n">
-        <v>401</v>
-      </c>
-      <c r="G342" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>bus18</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>21:37:00</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>22:01:00</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F343" t="n">
-        <v>401</v>
-      </c>
-      <c r="G343" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>bus20</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>22:05:00</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F344" t="n">
-        <v>401</v>
-      </c>
-      <c r="G344" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>bus19</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>22:07:00</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>22:31:00</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F345" t="n">
-        <v>401</v>
-      </c>
-      <c r="G345" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>bus17</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>22:35:00</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F346" t="n">
-        <v>401</v>
-      </c>
-      <c r="G346" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>bus20</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>22:37:00</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>23:01:00</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F347" t="n">
-        <v>401</v>
-      </c>
-      <c r="G347" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>bus15</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>23:05:00</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F348" t="n">
-        <v>401</v>
-      </c>
-      <c r="G348" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>bus17</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>23:07:00</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>23:31:00</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F349" t="n">
-        <v>401</v>
-      </c>
-      <c r="G349" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>bus16</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>23:35:00</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F350" t="n">
-        <v>401</v>
-      </c>
-      <c r="G350" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>bus15</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>23:37:00</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>00:01:00</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F351" t="n">
-        <v>401</v>
-      </c>
-      <c r="G351" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>bus14</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>00:01:00</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>00:26:00</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F352" t="n">
-        <v>401</v>
-      </c>
-      <c r="G352" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>bus16</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>00:09:00</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>00:33:00</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F353" t="n">
-        <v>401</v>
-      </c>
-      <c r="G353" t="n">
-        <v>10.8036</v>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>bus18</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>ehvapt</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>00:31:00</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>00:56:00</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F354" t="n">
-        <v>401</v>
-      </c>
-      <c r="G354" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>bus14</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>

--- a/Improved_Bus_Planning_version_B.xlsx
+++ b/Improved_Bus_Planning_version_B.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start location</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end location</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>start time</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>end time</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>activity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>line</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>energy consumption</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
